--- a/data/roster.xlsx
+++ b/data/roster.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -424,212 +424,246 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v/>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Jack</v>
+        <v>C1C Jack P. Tierney</v>
       </c>
       <c r="C2" t="str">
         <v>CB</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>2027</v>
       </c>
       <c r="E2" t="str">
         <v>Y</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v/>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>RJ</v>
+        <v>C1C Logan T Cook</v>
       </c>
       <c r="C3" t="str">
+        <v>CB</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2027</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>C1C Ryan S. Sansano</v>
+      </c>
+      <c r="C4" t="str">
+        <v>LW</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2027</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>C1C Zachary D. Crane</v>
+      </c>
+      <c r="C5" t="str">
+        <v>GK</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2027</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>C1C Robert W. Garrett IV</v>
+      </c>
+      <c r="C6" t="str">
         <v>LB</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="B4" t="str">
-        <v>Ryan</v>
-      </c>
-      <c r="C4" t="str">
+      <c r="D6" t="str">
+        <v>2027</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>C1C Troy E. Miller</v>
+      </c>
+      <c r="C7" t="str">
         <v>RW</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v>Roman</v>
-      </c>
-      <c r="C5" t="str">
+      <c r="D7" t="str">
+        <v>2027</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>C2C Darian K. Presley</v>
+      </c>
+      <c r="C8" t="str">
+        <v>CB</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2028</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>C2C Roman E. Trice</v>
+      </c>
+      <c r="C9" t="str">
         <v>P</v>
       </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
-      <c r="B6" t="str">
-        <v>Charlie</v>
-      </c>
-      <c r="C6" t="str">
-        <v>LW</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v>Evan</v>
-      </c>
-      <c r="C7" t="str">
-        <v>RB</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
-        <v>Barrett</v>
-      </c>
-      <c r="C8" t="str">
-        <v>LB</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v>Sean</v>
-      </c>
-      <c r="C9" t="str">
-        <v>LW</v>
-      </c>
       <c r="D9" t="str">
-        <v/>
+        <v>2028</v>
       </c>
       <c r="E9" t="str">
         <v>Y</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v/>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Christian</v>
+        <v>C3C Ian P. Cavendish</v>
       </c>
       <c r="C10" t="str">
-        <v>RW</v>
+        <v>CB</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>2029</v>
       </c>
       <c r="E10" t="str">
         <v>Y</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v/>
+      <c r="A11">
+        <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Ben</v>
+        <v>C3C Evan M. Feller</v>
       </c>
       <c r="C11" t="str">
+        <v>CB</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2029</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>C3C Tyler J. Ferguson</v>
+      </c>
+      <c r="C12" t="str">
         <v>P</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v/>
-      </c>
-      <c r="B12" t="str">
-        <v>Corn</v>
-      </c>
-      <c r="C12" t="str">
-        <v>GK</v>
-      </c>
       <c r="D12" t="str">
-        <v/>
+        <v>2029</v>
       </c>
       <c r="E12" t="str">
         <v>Y</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v/>
+      <c r="A13">
+        <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Crane</v>
+        <v>C3C Charles B. Forth</v>
       </c>
       <c r="C13" t="str">
-        <v>GK</v>
+        <v>CB</v>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>2029</v>
       </c>
       <c r="E13" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>C3C Barrett S. Waldvogel</v>
+      </c>
+      <c r="C14" t="str">
+        <v>CB</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2029</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>C3C Sean W. Windell</v>
+      </c>
+      <c r="C15" t="str">
+        <v>CB</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2029</v>
+      </c>
+      <c r="E15" t="str">
         <v>Y</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/roster.xlsx
+++ b/data/roster.xlsx
@@ -397,10 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
     <col min="3" max="3" width="6.83203125" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" customWidth="1"/>
@@ -661,9 +661,26 @@
         <v>Y</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>C3C Henry J. Listanowsky</v>
+      </c>
+      <c r="C16" t="str">
+        <v>LB</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2029</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Y</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/roster.xlsx
+++ b/data/roster.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -678,9 +678,26 @@
         <v>Y</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>C2C Riley W. Lanham</v>
+      </c>
+      <c r="C17" t="str">
+        <v>P</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2028</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Y</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/roster.xlsx
+++ b/data/roster.xlsx
@@ -618,7 +618,7 @@
         <v>C3C Charles B. Forth</v>
       </c>
       <c r="C13" t="str">
-        <v>CB</v>
+        <v>RW</v>
       </c>
       <c r="D13" t="str">
         <v>2029</v>
@@ -635,7 +635,7 @@
         <v>C3C Barrett S. Waldvogel</v>
       </c>
       <c r="C14" t="str">
-        <v>CB</v>
+        <v>LB</v>
       </c>
       <c r="D14" t="str">
         <v>2029</v>
